--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0032.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0032.xlsx
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Ta không có thời gian...</t>
+          <t>Tao không có thời gian...</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Không quan trọng. Ta sẽ trả. Bằng bất cứ giá nào.</t>
+          <t>Không quan trọng. Tao sẽ trả. Bằng bất cứ giá nào.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>...Thủy Triều Hắc Ám không lấy đi cô ấy. Cô ấy đã cố gắng chờ đến khi ta tới.</t>
+          <t>...Thủy Triều Hắc Ám không lấy đi cô ấy. Cô ấy đã cố gắng chờ đến khi tao tới.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Tất nhiên rồi.</t>
+          <t>Đương nhiên.</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Không cần vung kiếm hay cau có thế, {Male=anh;Female=chị} {PlayerName}. Ta đến đây không phải do tự nguyện. Chính Lumenstone đã đưa ta tới.</t>
+          <t>Không cần vung kiếm hay cau có thế, {Male=Mr.;Female=Ms.} {PlayerName}. Ta đến đây không phải do tự nguyện. Chính Lumenstone đã đưa ta tới.</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Thật lòng, đúng vậy. Ta &lt;i&gt;rất&lt;/i&gt; thất vọng.</t>
+          <t>Thật lòng, đúng vậy. Tao &lt;i&gt;rất&lt;/i&gt; thất vọng.</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Ôi, {Male=anh;Female=chị} {PlayerName}.</t>
+          <t>Ôi, {Male=Mr.;Female=Ms.} {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Ta không đến đây để xem trò hề của ngươi đâu.</t>
+          <t>Tao không đến đây để xem trò hề của mày đâu.</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Ngươi có vẻ còn ngu hơn cả đám ác nhân đấy, mà lại liều lĩnh gấp đôi lũ ngốc nửa vời.</t>
+          <t>Mày có vẻ còn ngu hơn cả đám ác nhân đấy, mà lại liều lĩnh gấp đôi lũ ngốc nửa vời.</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}? Là cậu à? Ôi trời! Ở đây này!</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}? Là cậu à? Ôi trời! Ở đây này!</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Phù, lại là cậu à, {PlayerName}. Làm ta giật cả mình…</t>
+          <t>Phù, lại là cậu à, {PlayerName}. Làm tao giật cả mình…</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Sao mặt thế hả, {PlayerName}? Ta lại nói gì sai à?</t>
+          <t>Sao mặt thế hả, {PlayerName}? Tao lại nói gì sai à?</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Ừm... Ta sẽ suy nghĩ kỹ trước khi quyết định.</t>
+          <t>Ừm... Tao sẽ suy nghĩ kỹ trước khi quyết định.</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Ôi, {Male=anh;Female=chị} {PlayerName}, {Male=anh;Female=chị} thật quá nhân từ… tha thứ cho kẻ tội đồ như tôi, chìm đắm trong tội lỗi đến thế này.</t>
+          <t>Ôi, {Male=Mr.;Female=Ms.} {PlayerName}, bạn thật quá nhân từ… tha thứ cho kẻ tội đồ như tôi, chìm đắm trong tội lỗi đến thế này.</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Đây! Chính cái này đây, là thứ ta muốn. Được chứng kiến trận đấu vĩ đại nhất của Septimont hết lần này đến lần khác!</t>
+          <t>Đây! Chính cái này đây, là thứ tao muốn. Được chứng kiến trận đấu vĩ đại nhất của Septimont hết lần này đến lần khác!</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Không ngờ lại gặp cậu ở đây! Sentinel đưa cậu đến à, hay... ừm, cậu nghe thấy tiếng ta kêu cứu?</t>
+          <t>Không ngờ lại gặp cậu ở đây! Sentinel đưa cậu đến à, hay... ừm, cậu nghe thấy tiếng tao kêu cứu?</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Haha, may mắn thế! Ta cứ tưởng mình mắc kẹt ở đây mãi mãi rồi.</t>
+          <t>Haha, may mắn thế! Tao cứ tưởng mình mắc kẹt ở đây mãi mãi rồi.</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Ngươi nghĩ ta tin được sao? Một kẻ phàm tục lại cưỡng lại được Hắc Triều?</t>
+          <t>Mày nghĩ tao tin được sao? Một kẻ phàm tục lại cưỡng lại được Hắc Triều?</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Thật ra, anh Medulius đã cứu ta khi ta lạc ở Hẻm núi Mournfell này, {Male=anh;Female=chị} {PlayerName}. Chúng ta đang chuẩn bị rời đi đây.</t>
+          <t>Thật ra, anh Medulius đã cứu ta khi ta lạc ở Hẻm núi Mournfell này, {Male=Mr.;Female=Ms.} {PlayerName}. Chúng ta đang chuẩn bị rời đi đây.</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Cậu dám cả gan nhỉ? Đến cả Dark Tide cũng chẳng khiến cậu run sợ à?</t>
+          <t>Mày dám cả gan nhỉ? Đến cả Dark Tide cũng chẳng khiến mày run sợ à?</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Đúng là Phrolova. Đúng như ta nghĩ.</t>
+          <t>Đúng là Phrolova. Đúng như tao nghĩ.</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Đã quá lâu rồi, {Male=ngài;Female=cô} ạ. Sóng Thủy Triều đã cuốn sạch mọi ký ức của ta.</t>
+          <t>Đã quá lâu rồi, {Male=Sir;Female=Miss} ạ. Sóng Thủy Triều đã cuốn sạch mọi ký ức của ta.</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Ta sẽ quyết định sau khi nói chuyện với cô ấy.</t>
+          <t>Tao sẽ quyết định sau khi nói chuyện với cô ấy.</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Tại sao?</t>
+          <t>Sao vậy?</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Hắn đưa ta lên một con thuyền khác, bảo là đi Ragunna, nhưng rõ ràng là không phải! Nếu không thì ta đã không đứng đây ở Septimont rồi!</t>
+          <t>Hắn đưa tao lên một con thuyền khác, bảo là đi Ragunna, nhưng rõ ràng là không phải! Nếu không thì tao đã không đứng đây ở Septimont rồi!</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Yes...</t>
+          <t>Ừ...</t>
         </is>
       </c>
     </row>
